--- a/HW2/HW2_grades.xlsx
+++ b/HW2/HW2_grades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Desktop/GitHub/2026_Computational-Modeling/HW2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2797BF37-4225-7D45-B42A-B5B7D1178D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2743AE-70FF-764D-91F8-0EB79D759824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2600" yWindow="760" windowWidth="27640" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -713,6 +713,466 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>(c) model comparison</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Q1)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">MLE_LSE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> LSE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방법에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>덮어씌워짐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (sse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> return</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> value name </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mle_~, model comparison </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(a): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (-21)
+(b): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (-21)
+(c): discussion </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맞으나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보고로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작성함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. (-8)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1046,7 +1506,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">했음 (-3)
+      <t xml:space="preserve">했음 (-3; -1.5 for each)
 </t>
     </r>
     <r>
@@ -1196,10 +1656,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(c) model comparison</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1218,7 +1674,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">)
-(b): </t>
+(b): ra_noRA </t>
     </r>
     <r>
       <rPr>
@@ -1525,14 +1981,6 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Q1)
-MLE_LSE 코드에서 LSE 방법에 mle 코드가 덮어씌워짐 (sse를 return하는 코드의 value name 이 mle_~, model comparison 할 때 이 코드들이 사용됨)
-(a): 보고 잘못됨 (-21)
-(b): 보고 잘못됨 (-21)
-(c): discussion 은 맞으나 잘못된 보고로 작성함. (-8)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1540,7 +1988,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1582,6 +2030,19 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
       <name val="Malgun Gothic"/>
       <family val="2"/>
       <charset val="129"/>
@@ -1712,12 +2173,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1736,6 +2191,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2083,7 +2544,7 @@
       <c r="I1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="19" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2115,8 +2576,8 @@
       <c r="I2" s="3">
         <v>117.5</v>
       </c>
-      <c r="J2" s="22" t="s">
-        <v>70</v>
+      <c r="J2" s="20" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="86" customHeight="1">
@@ -2147,7 +2608,7 @@
       <c r="I3" s="3">
         <v>130</v>
       </c>
-      <c r="J3" s="23"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="114" customHeight="1">
       <c r="A4" s="15" t="s">
@@ -2177,8 +2638,8 @@
       <c r="I4" s="3">
         <v>97</v>
       </c>
-      <c r="J4" s="22" t="s">
-        <v>68</v>
+      <c r="J4" s="20" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="25" customHeight="1">
@@ -2209,7 +2670,7 @@
       <c r="I5" s="3">
         <v>130</v>
       </c>
-      <c r="J5" s="22"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="119" customHeight="1">
       <c r="A6" s="15" t="s">
@@ -2239,9 +2700,9 @@
       <c r="I6" s="3">
         <v>130</v>
       </c>
-      <c r="J6" s="24"/>
+      <c r="J6" s="22"/>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="96" customHeight="1">
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="131" customHeight="1">
       <c r="A7" s="15" t="s">
         <v>8</v>
       </c>
@@ -2269,8 +2730,8 @@
       <c r="I7" s="3">
         <v>80</v>
       </c>
-      <c r="J7" s="25" t="s">
-        <v>71</v>
+      <c r="J7" s="23" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="47" customHeight="1">
@@ -2301,7 +2762,7 @@
       <c r="I8" s="3">
         <v>130</v>
       </c>
-      <c r="J8" s="22"/>
+      <c r="J8" s="20"/>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="41" customHeight="1">
       <c r="A9" s="15" t="s">
@@ -2331,7 +2792,7 @@
       <c r="I9" s="3">
         <v>130</v>
       </c>
-      <c r="J9" s="22"/>
+      <c r="J9" s="20"/>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="25" customHeight="1">
       <c r="A10" s="10"/>
@@ -2343,7 +2804,7 @@
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
-      <c r="J10" s="26"/>
+      <c r="J10" s="24"/>
     </row>
     <row r="11" spans="1:10">
       <c r="J11" s="4" t="s">
@@ -2351,10 +2812,10 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="19"/>
+      <c r="B12" s="26"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="6" t="s">
@@ -2375,7 +2836,7 @@
       <c r="B14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="18" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2477,7 +2938,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" s="13">
         <v>10</v>

--- a/HW2/HW2_grades.xlsx
+++ b/HW2/HW2_grades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Desktop/GitHub/2026_Computational-Modeling/HW2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2743AE-70FF-764D-91F8-0EB79D759824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FBAE149-9E75-3843-A335-C3743042D960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="760" windowWidth="27640" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2600" yWindow="1860" windowWidth="27640" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -718,6 +718,817 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Q1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- MLE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. HW1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제출한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌렸을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정답임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. 
+(b) BIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> pow2, exp2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">코드에서만 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">k_ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숫자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용 (둘다 "2" 사용)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나머지는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> k_ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">했음 (-3; -1.5 for each)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Q2)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- subject </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>별</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> loop </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맞음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Q3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+(b): ra_noRA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> lambda boundary </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (0~10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 0~5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) --&gt; sub3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> parameter estimation </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. (-1; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+(c): ra_noRA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AIC, BIC sum </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>틀림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (-1.5; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Q1)
 </t>
     </r>
@@ -1024,16 +1835,16 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>잘못됨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (-21)
+      <t xml:space="preserve">잘못됨, 코드 오류 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(-10.5)
 (b): </t>
     </r>
     <r>
@@ -1063,16 +1874,16 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>잘못됨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (-21)
+      <t>잘못됨, 코드 오류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  (-10.5)
 (c): discussion </t>
     </r>
     <r>
@@ -1168,451 +1979,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>. (-8)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Q1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-- MLE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>코드가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. HW1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제출한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>코드로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>돌렸을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>때</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정답임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. 
-(b) BIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>코드에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> pow2, exp2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">코드에서만 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">k_ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>안하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>숫자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용 (둘다 "2" 사용)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나머지는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> k_ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">했음 (-3; -1.5 for each)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Q2)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">- subject </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>별</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> loop </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>않음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">. </t>
     </r>
     <r>
@@ -1623,67 +1989,6 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>보고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맞음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Q3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-(b): ra_noRA </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
       <t>코드</t>
     </r>
     <r>
@@ -1703,25 +2008,6 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> lambda boundary </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
       <t>오류</t>
     </r>
     <r>
@@ -1731,255 +2017,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (0~10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인데</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 0~5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>설정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>) --&gt; sub3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> parameter estimation </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>잘못됨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. (-1; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>코드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오류</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-(c): ra_noRA </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> AIC, BIC sum </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>틀림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (-1.5; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>코드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오류</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
+      <t xml:space="preserve"> (-4)</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2571,13 +2609,13 @@
         <v>50</v>
       </c>
       <c r="H2" s="3">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="I2" s="3">
-        <v>117.5</v>
+        <v>127.5</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="86" customHeight="1">
@@ -2639,7 +2677,7 @@
         <v>97</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="25" customHeight="1">
@@ -2731,7 +2769,7 @@
         <v>80</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="47" customHeight="1">

--- a/HW2/HW2_grades.xlsx
+++ b/HW2/HW2_grades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Desktop/GitHub/2026_Computational-Modeling/HW2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FBAE149-9E75-3843-A335-C3743042D960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6468413-DEB0-E046-9BDB-AE6AEF7A16F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="1860" windowWidth="27640" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1700" yWindow="700" windowWidth="27640" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2757,7 +2757,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="16">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G7" s="16">
         <v>50</v>
@@ -2766,7 +2766,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="3">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="J7" s="23" t="s">
         <v>71</v>
